--- a/V44.xlsx
+++ b/V44.xlsx
@@ -8,13 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oskar\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676ABAFE-C3D0-4C84-9F38-DE79DF9AC91F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A28776-6EB3-418A-A7CF-E6FEBD41AF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="30648" windowHeight="18517" activeTab="1" xr2:uid="{D5BDAF23-79F4-4D7D-A14F-26496FE39CDA}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="30648" windowHeight="18517" activeTab="7" xr2:uid="{D5BDAF23-79F4-4D7D-A14F-26496FE39CDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Teil 1" sheetId="1" r:id="rId1"/>
     <sheet name="Teil 2" sheetId="2" r:id="rId2"/>
+    <sheet name="11" sheetId="3" r:id="rId3"/>
+    <sheet name="12" sheetId="4" r:id="rId4"/>
+    <sheet name="21" sheetId="5" r:id="rId5"/>
+    <sheet name="22" sheetId="6" r:id="rId6"/>
+    <sheet name="31" sheetId="7" r:id="rId7"/>
+    <sheet name="32" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="30">
   <si>
     <t>V44</t>
   </si>
@@ -135,7 +141,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -174,12 +180,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1464,7 +1469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89396F1D-3EB9-4E26-BDDF-038233605A4B}">
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1954,7 +1959,7 @@
       <c r="S11" t="s">
         <v>16</v>
       </c>
-      <c r="T11" s="4">
+      <c r="T11" s="2">
         <f>ROUND(Q11/R11,3)</f>
         <v>8.5999999999999993E-2</v>
       </c>
@@ -2007,7 +2012,7 @@
       <c r="S12" t="s">
         <v>16</v>
       </c>
-      <c r="T12" s="4">
+      <c r="T12" s="2">
         <f t="shared" ref="T12:T15" si="6">ROUND(Q12/R12,3)</f>
         <v>7.4999999999999997E-2</v>
       </c>
@@ -2060,7 +2065,7 @@
       <c r="S13" t="s">
         <v>16</v>
       </c>
-      <c r="T13" s="4">
+      <c r="T13" s="2">
         <f t="shared" si="6"/>
         <v>8.7999999999999995E-2</v>
       </c>
@@ -2113,7 +2118,7 @@
       <c r="S14" t="s">
         <v>16</v>
       </c>
-      <c r="T14" s="4">
+      <c r="T14" s="2">
         <f t="shared" si="6"/>
         <v>9.7000000000000003E-2</v>
       </c>
@@ -2166,13 +2171,532 @@
       <c r="S15" t="s">
         <v>16</v>
       </c>
-      <c r="T15" s="4">
+      <c r="T15" s="2">
         <f t="shared" si="6"/>
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="U15">
         <f t="shared" si="5"/>
         <v>0.82</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.37</v>
+      </c>
+      <c r="D21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="2">
+        <v>0.44</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="D26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="2">
+        <v>0.49</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.90800000000000003</v>
+      </c>
+      <c r="D28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B29" s="2">
+        <v>0.78</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1.484</v>
+      </c>
+      <c r="D29" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B30" s="2">
+        <v>1.02</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1.8979999999999999</v>
+      </c>
+      <c r="D30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="3">
+        <v>0.66</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="D32" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="3">
+        <v>0.124</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="D33" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="3">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="D34" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B35" s="3">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="D35" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B36" s="3">
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="D36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="C38" s="3">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="D38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="C39" s="3">
+        <v>0.438</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B40" s="2">
+        <v>0.24</v>
+      </c>
+      <c r="C40" s="3">
+        <v>0.73899999999999999</v>
+      </c>
+      <c r="D40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="F40" s="2"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B41" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="C41" s="3">
+        <v>0.85299999999999998</v>
+      </c>
+      <c r="D41" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B42" s="2">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="C42" s="3">
+        <v>1.778</v>
+      </c>
+      <c r="D42" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="F42" s="2"/>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B44" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="C44" s="3">
+        <v>0.31</v>
+      </c>
+      <c r="D44" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B45" s="3">
+        <v>5.5E-2</v>
+      </c>
+      <c r="C45" s="3">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="D45" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B46" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="C46" s="3">
+        <v>0.93</v>
+      </c>
+      <c r="D46" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B47" s="3">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="C47" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="D47" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B48" s="3">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="C48" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="D48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50">
+        <v>0.03</v>
+      </c>
+      <c r="C50">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="D50" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51">
+        <v>0.05</v>
+      </c>
+      <c r="C51">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="D51" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52">
+        <v>0.09</v>
+      </c>
+      <c r="C52">
+        <v>1.024</v>
+      </c>
+      <c r="D52" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C53">
+        <v>1.4430000000000001</v>
+      </c>
+      <c r="D53" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54">
+        <v>0.19</v>
+      </c>
+      <c r="C54">
+        <v>1.948</v>
+      </c>
+      <c r="D54" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54">
+        <v>0.25600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2507,4 +3031,613 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BECB2E4-71D2-4163-84E2-5091583A67C2}">
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>0.44</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="B6" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E12" s="2"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E18" s="2"/>
+    </row>
+    <row r="20" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E24" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75C82E37-2039-4E6E-9DEB-3231A45CB898}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>0.49</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.90800000000000003</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>0.78</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1.484</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>1.02</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1.8979999999999999</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{752C6791-DD73-4578-9720-693A6C2D1C39}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>0.66</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>0.124</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4573A3C-3AD5-409E-B93C-37FADC4AC910}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.438</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>0.24</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.73899999999999999</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.85299999999999998</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1.778</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>0.58699999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{022916CA-667D-4499-A70B-DE198CF5071D}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0.31</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>5.5E-2</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.93</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C1F06F3-EAC2-4B92-AACA-FA162CDAD892}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0.03</v>
+      </c>
+      <c r="B2">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>0.05</v>
+      </c>
+      <c r="B3">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>0.09</v>
+      </c>
+      <c r="B4">
+        <v>1.024</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="B5">
+        <v>1.4430000000000001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>0.19</v>
+      </c>
+      <c r="B6">
+        <v>1.948</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>0.25600000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/V44.xlsx
+++ b/V44.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oskar\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c126945bea7d3965/UNI/AP1/GitHub/AP1-Gruppe-143/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A28776-6EB3-418A-A7CF-E6FEBD41AF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{33A28776-6EB3-418A-A7CF-E6FEBD41AF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{122420A1-2CA2-44DA-B9AB-71738CF2D702}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="30648" windowHeight="18517" activeTab="7" xr2:uid="{D5BDAF23-79F4-4D7D-A14F-26496FE39CDA}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="30648" windowHeight="18517" activeTab="3" xr2:uid="{D5BDAF23-79F4-4D7D-A14F-26496FE39CDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Teil 1" sheetId="1" r:id="rId1"/>
@@ -3040,10 +3040,10 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
         <v>7</v>
